--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -1183,45 +1183,59 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129074896</v>
+        <v>129073070</v>
       </c>
       <c r="B7" t="n">
-        <v>79653</v>
+        <v>92811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469691</v>
+        <v>469736</v>
       </c>
       <c r="R7" t="n">
-        <v>6860502</v>
+        <v>6860324</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129073823</v>
+        <v>129074896</v>
       </c>
       <c r="B8" t="n">
-        <v>78791</v>
+        <v>79653</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,21 +1305,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469769</v>
+        <v>469691</v>
       </c>
       <c r="R8" t="n">
-        <v>6860351</v>
+        <v>6860502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,59 +1391,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129073070</v>
+        <v>129073823</v>
       </c>
       <c r="B9" t="n">
-        <v>92811</v>
+        <v>78791</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469736</v>
+        <v>469769</v>
       </c>
       <c r="R9" t="n">
-        <v>6860324</v>
+        <v>6860351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129072852</v>
+        <v>129075376</v>
       </c>
       <c r="B14" t="n">
-        <v>78792</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,34 +1887,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469681</v>
+        <v>469623</v>
       </c>
       <c r="R14" t="n">
-        <v>6860335</v>
+        <v>6860454</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,6 +1947,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1973,10 +1978,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129075376</v>
+        <v>129072852</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>78792</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1984,34 +1989,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469623</v>
+        <v>469681</v>
       </c>
       <c r="R15" t="n">
-        <v>6860454</v>
+        <v>6860335</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2044,11 +2049,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129073710</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129074043</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>129073070</v>
       </c>
       <c r="B7" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129076255</v>
+        <v>129075167</v>
       </c>
       <c r="B10" t="n">
-        <v>78700</v>
+        <v>78792</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,21 +1499,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469608</v>
+        <v>469625</v>
       </c>
       <c r="R10" t="n">
-        <v>6860373</v>
+        <v>6860490</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129075167</v>
+        <v>129076255</v>
       </c>
       <c r="B11" t="n">
-        <v>78792</v>
+        <v>78700</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469625</v>
+        <v>469608</v>
       </c>
       <c r="R11" t="n">
-        <v>6860490</v>
+        <v>6860373</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1978,45 +1978,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129072852</v>
+        <v>129073789</v>
       </c>
       <c r="B15" t="n">
-        <v>78792</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469681</v>
+        <v>469761</v>
       </c>
       <c r="R15" t="n">
-        <v>6860335</v>
+        <v>6860341</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2075,54 +2084,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129073789</v>
+        <v>129072852</v>
       </c>
       <c r="B16" t="n">
-        <v>98651</v>
+        <v>78792</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469761</v>
+        <v>469681</v>
       </c>
       <c r="R16" t="n">
-        <v>6860341</v>
+        <v>6860335</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2666,45 +2666,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129073686</v>
+        <v>129074106</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469742</v>
+        <v>469787</v>
       </c>
       <c r="R22" t="n">
-        <v>6860327</v>
+        <v>6860379</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,11 +2746,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2768,54 +2772,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129074106</v>
+        <v>129073686</v>
       </c>
       <c r="B23" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469787</v>
+        <v>469742</v>
       </c>
       <c r="R23" t="n">
-        <v>6860379</v>
+        <v>6860327</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,6 +2843,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129073710</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129074043</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>129073324</v>
       </c>
       <c r="B5" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>129074721</v>
       </c>
       <c r="B6" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>129073070</v>
       </c>
       <c r="B7" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>129074896</v>
       </c>
       <c r="B8" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>129073823</v>
       </c>
       <c r="B9" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129075167</v>
       </c>
       <c r="B10" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>129076255</v>
       </c>
       <c r="B11" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129075209</v>
+        <v>129074218</v>
       </c>
       <c r="B12" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469625</v>
+        <v>469807</v>
       </c>
       <c r="R12" t="n">
-        <v>6860485</v>
+        <v>6860393</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129074218</v>
+        <v>129075209</v>
       </c>
       <c r="B13" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469807</v>
+        <v>469625</v>
       </c>
       <c r="R13" t="n">
-        <v>6860393</v>
+        <v>6860485</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129075376</v>
+        <v>129072852</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>78793</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,34 +1887,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469623</v>
+        <v>469681</v>
       </c>
       <c r="R14" t="n">
-        <v>6860454</v>
+        <v>6860335</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,11 +1947,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1978,54 +1973,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129073789</v>
+        <v>129075376</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469761</v>
+        <v>469623</v>
       </c>
       <c r="R15" t="n">
-        <v>6860341</v>
+        <v>6860454</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2058,6 +2044,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2084,45 +2075,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129072852</v>
+        <v>129073789</v>
       </c>
       <c r="B16" t="n">
-        <v>78792</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469681</v>
+        <v>469761</v>
       </c>
       <c r="R16" t="n">
-        <v>6860335</v>
+        <v>6860341</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2181,32 +2181,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129074684</v>
+        <v>129074551</v>
       </c>
       <c r="B17" t="n">
-        <v>80167</v>
+        <v>79625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>469714</v>
+        <v>469743</v>
       </c>
       <c r="R17" t="n">
-        <v>6860460</v>
+        <v>6860417</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,32 +2278,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129074551</v>
+        <v>129074684</v>
       </c>
       <c r="B18" t="n">
-        <v>79624</v>
+        <v>80168</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469743</v>
+        <v>469714</v>
       </c>
       <c r="R18" t="n">
-        <v>6860417</v>
+        <v>6860460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2378,7 +2378,7 @@
         <v>129074540</v>
       </c>
       <c r="B19" t="n">
-        <v>78042</v>
+        <v>78043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129074919</v>
       </c>
       <c r="B20" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>129075085</v>
       </c>
       <c r="B21" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,54 +2666,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129074106</v>
+        <v>129073686</v>
       </c>
       <c r="B22" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469787</v>
+        <v>469742</v>
       </c>
       <c r="R22" t="n">
-        <v>6860379</v>
+        <v>6860327</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,6 +2737,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2772,45 +2768,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129073686</v>
+        <v>129074106</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469742</v>
+        <v>469787</v>
       </c>
       <c r="R23" t="n">
-        <v>6860327</v>
+        <v>6860379</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,11 +2848,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2877,7 +2877,7 @@
         <v>129075590</v>
       </c>
       <c r="B24" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>129072966</v>
       </c>
       <c r="B25" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -1488,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129075167</v>
+        <v>129076255</v>
       </c>
       <c r="B10" t="n">
-        <v>78793</v>
+        <v>78701</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,21 +1499,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469625</v>
+        <v>469608</v>
       </c>
       <c r="R10" t="n">
-        <v>6860490</v>
+        <v>6860373</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129076255</v>
+        <v>129075167</v>
       </c>
       <c r="B11" t="n">
-        <v>78701</v>
+        <v>78793</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469608</v>
+        <v>469625</v>
       </c>
       <c r="R11" t="n">
-        <v>6860373</v>
+        <v>6860490</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129074218</v>
+        <v>129075209</v>
       </c>
       <c r="B12" t="n">
         <v>78701</v>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469807</v>
+        <v>469625</v>
       </c>
       <c r="R12" t="n">
-        <v>6860393</v>
+        <v>6860485</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,7 +1779,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129075209</v>
+        <v>129074218</v>
       </c>
       <c r="B13" t="n">
         <v>78701</v>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469625</v>
+        <v>469807</v>
       </c>
       <c r="R13" t="n">
-        <v>6860485</v>
+        <v>6860393</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129072852</v>
+        <v>129075376</v>
       </c>
       <c r="B14" t="n">
-        <v>78793</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,34 +1887,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469681</v>
+        <v>469623</v>
       </c>
       <c r="R14" t="n">
-        <v>6860335</v>
+        <v>6860454</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,6 +1947,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1973,45 +1978,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129075376</v>
+        <v>129073789</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469623</v>
+        <v>469761</v>
       </c>
       <c r="R15" t="n">
-        <v>6860454</v>
+        <v>6860341</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2044,11 +2058,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2075,54 +2084,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129073789</v>
+        <v>129072852</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>78793</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469761</v>
+        <v>469681</v>
       </c>
       <c r="R16" t="n">
-        <v>6860341</v>
+        <v>6860335</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2181,32 +2181,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129074551</v>
+        <v>129074684</v>
       </c>
       <c r="B17" t="n">
-        <v>79625</v>
+        <v>80168</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>469743</v>
+        <v>469714</v>
       </c>
       <c r="R17" t="n">
-        <v>6860417</v>
+        <v>6860460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,32 +2278,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129074684</v>
+        <v>129074551</v>
       </c>
       <c r="B18" t="n">
-        <v>80168</v>
+        <v>79625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6461</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469714</v>
+        <v>469743</v>
       </c>
       <c r="R18" t="n">
-        <v>6860460</v>
+        <v>6860417</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2666,45 +2666,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129073686</v>
+        <v>129074106</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469742</v>
+        <v>469787</v>
       </c>
       <c r="R22" t="n">
-        <v>6860327</v>
+        <v>6860379</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,11 +2746,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2768,54 +2772,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129074106</v>
+        <v>129073686</v>
       </c>
       <c r="B23" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469787</v>
+        <v>469742</v>
       </c>
       <c r="R23" t="n">
-        <v>6860379</v>
+        <v>6860327</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,6 +2843,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -1876,45 +1876,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129075376</v>
+        <v>129073789</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469623</v>
+        <v>469761</v>
       </c>
       <c r="R14" t="n">
-        <v>6860454</v>
+        <v>6860341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,11 +1956,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1978,54 +1982,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129073789</v>
+        <v>129072852</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>78793</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469761</v>
+        <v>469681</v>
       </c>
       <c r="R15" t="n">
-        <v>6860341</v>
+        <v>6860335</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2084,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129072852</v>
+        <v>129075376</v>
       </c>
       <c r="B16" t="n">
-        <v>78793</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2095,34 +2090,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469681</v>
+        <v>469623</v>
       </c>
       <c r="R16" t="n">
-        <v>6860335</v>
+        <v>6860454</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,6 +2150,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,45 +781,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129076566</v>
+        <v>129074043</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469689</v>
+        <v>469786</v>
       </c>
       <c r="R3" t="n">
-        <v>6860378</v>
+        <v>6860361</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,54 +887,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129074043</v>
+        <v>129076566</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469786</v>
+        <v>469689</v>
       </c>
       <c r="R4" t="n">
-        <v>6860361</v>
+        <v>6860378</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +958,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1183,59 +1183,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129073070</v>
+        <v>129074896</v>
       </c>
       <c r="B7" t="n">
-        <v>92819</v>
+        <v>79654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469736</v>
+        <v>469691</v>
       </c>
       <c r="R7" t="n">
-        <v>6860324</v>
+        <v>6860502</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,10 +1280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129074896</v>
+        <v>129073823</v>
       </c>
       <c r="B8" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,21 +1291,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1329,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469691</v>
+        <v>469769</v>
       </c>
       <c r="R8" t="n">
-        <v>6860502</v>
+        <v>6860351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,45 +1377,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129073823</v>
+        <v>129073070</v>
       </c>
       <c r="B9" t="n">
-        <v>78792</v>
+        <v>92819</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469769</v>
+        <v>469736</v>
       </c>
       <c r="R9" t="n">
-        <v>6860351</v>
+        <v>6860324</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1876,54 +1876,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129073789</v>
+        <v>129072852</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>78793</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469761</v>
+        <v>469681</v>
       </c>
       <c r="R14" t="n">
-        <v>6860341</v>
+        <v>6860335</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,45 +1973,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129072852</v>
+        <v>129073789</v>
       </c>
       <c r="B15" t="n">
-        <v>78793</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469681</v>
+        <v>469761</v>
       </c>
       <c r="R15" t="n">
-        <v>6860335</v>
+        <v>6860341</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3066,6 +3066,1087 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129240565</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78795</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>469806</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6860413</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129240619</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98667</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>469801</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6860453</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129240256</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79656</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>469555</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6860433</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129240501</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78795</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>469685</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6860410</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129240555</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78703</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>353</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>469816</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6860403</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129240241</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78703</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>353</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>469557</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6860436</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129240472</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78703</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>353</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>469672</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6860410</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129240219</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78795</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>469551</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6860399</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129242930</v>
+      </c>
+      <c r="B34" t="n">
+        <v>83013</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>469792</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6860485</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129243036</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>469792</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6860485</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129240407</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78703</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>353</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>469618</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6860428</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129073710</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,54 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129074043</v>
+        <v>129076566</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469786</v>
+        <v>469689</v>
       </c>
       <c r="R3" t="n">
-        <v>6860361</v>
+        <v>6860378</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,6 +852,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,45 +883,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129076566</v>
+        <v>129074043</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469689</v>
+        <v>469786</v>
       </c>
       <c r="R4" t="n">
-        <v>6860378</v>
+        <v>6860361</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,7 +992,7 @@
         <v>129073324</v>
       </c>
       <c r="B5" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>129074721</v>
       </c>
       <c r="B6" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,45 +1183,59 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129074896</v>
+        <v>129073070</v>
       </c>
       <c r="B7" t="n">
-        <v>79654</v>
+        <v>92826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469691</v>
+        <v>469736</v>
       </c>
       <c r="R7" t="n">
-        <v>6860502</v>
+        <v>6860324</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129073823</v>
+        <v>129074896</v>
       </c>
       <c r="B8" t="n">
-        <v>78792</v>
+        <v>79658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,21 +1305,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469769</v>
+        <v>469691</v>
       </c>
       <c r="R8" t="n">
-        <v>6860351</v>
+        <v>6860502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,59 +1391,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129073070</v>
+        <v>129073823</v>
       </c>
       <c r="B9" t="n">
-        <v>92819</v>
+        <v>78796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469736</v>
+        <v>469769</v>
       </c>
       <c r="R9" t="n">
-        <v>6860324</v>
+        <v>6860351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
         <v>129076255</v>
       </c>
       <c r="B10" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>129075167</v>
       </c>
       <c r="B11" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129075209</v>
+        <v>129074218</v>
       </c>
       <c r="B12" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469625</v>
+        <v>469807</v>
       </c>
       <c r="R12" t="n">
-        <v>6860485</v>
+        <v>6860393</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129074218</v>
+        <v>129075209</v>
       </c>
       <c r="B13" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469807</v>
+        <v>469625</v>
       </c>
       <c r="R13" t="n">
-        <v>6860393</v>
+        <v>6860485</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129072852</v>
+        <v>129075376</v>
       </c>
       <c r="B14" t="n">
-        <v>78793</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,34 +1887,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469681</v>
+        <v>469623</v>
       </c>
       <c r="R14" t="n">
-        <v>6860335</v>
+        <v>6860454</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,6 +1947,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,7 +1981,7 @@
         <v>129073789</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2079,10 +2084,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129075376</v>
+        <v>129072852</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>78797</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,34 +2095,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469623</v>
+        <v>469681</v>
       </c>
       <c r="R16" t="n">
-        <v>6860454</v>
+        <v>6860335</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,11 +2155,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2181,32 +2181,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129074684</v>
+        <v>129074551</v>
       </c>
       <c r="B17" t="n">
-        <v>80168</v>
+        <v>79629</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>469714</v>
+        <v>469743</v>
       </c>
       <c r="R17" t="n">
-        <v>6860460</v>
+        <v>6860417</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,32 +2278,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129074551</v>
+        <v>129074684</v>
       </c>
       <c r="B18" t="n">
-        <v>79625</v>
+        <v>80172</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469743</v>
+        <v>469714</v>
       </c>
       <c r="R18" t="n">
-        <v>6860417</v>
+        <v>6860460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2378,7 +2378,7 @@
         <v>129074540</v>
       </c>
       <c r="B19" t="n">
-        <v>78043</v>
+        <v>78047</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129074919</v>
       </c>
       <c r="B20" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>129075085</v>
       </c>
       <c r="B21" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>129074106</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>129073686</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>129075590</v>
       </c>
       <c r="B24" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>129072966</v>
       </c>
       <c r="B25" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>129240565</v>
       </c>
       <c r="B26" t="n">
-        <v>78795</v>
+        <v>78797</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>129240619</v>
       </c>
       <c r="B27" t="n">
-        <v>98667</v>
+        <v>98669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129240256</v>
+        <v>129240501</v>
       </c>
       <c r="B28" t="n">
-        <v>79656</v>
+        <v>78797</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3282,21 +3282,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469555</v>
+        <v>469685</v>
       </c>
       <c r="R28" t="n">
-        <v>6860433</v>
+        <v>6860410</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129240501</v>
+        <v>129240256</v>
       </c>
       <c r="B29" t="n">
-        <v>78795</v>
+        <v>79658</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469685</v>
+        <v>469555</v>
       </c>
       <c r="R29" t="n">
-        <v>6860410</v>
+        <v>6860433</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3468,7 +3468,7 @@
         <v>129240555</v>
       </c>
       <c r="B30" t="n">
-        <v>78703</v>
+        <v>78705</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>129240241</v>
       </c>
       <c r="B31" t="n">
-        <v>78703</v>
+        <v>78705</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>129240472</v>
       </c>
       <c r="B32" t="n">
-        <v>78703</v>
+        <v>78705</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>129240219</v>
       </c>
       <c r="B33" t="n">
-        <v>78795</v>
+        <v>78797</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>129242930</v>
       </c>
       <c r="B34" t="n">
-        <v>83013</v>
+        <v>83015</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>129240407</v>
       </c>
       <c r="B36" t="n">
-        <v>78703</v>
+        <v>78705</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -2181,32 +2181,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129074551</v>
+        <v>129074684</v>
       </c>
       <c r="B17" t="n">
-        <v>79629</v>
+        <v>80172</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>469743</v>
+        <v>469714</v>
       </c>
       <c r="R17" t="n">
-        <v>6860417</v>
+        <v>6860460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,32 +2278,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129074684</v>
+        <v>129074551</v>
       </c>
       <c r="B18" t="n">
-        <v>80172</v>
+        <v>79629</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6461</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469714</v>
+        <v>469743</v>
       </c>
       <c r="R18" t="n">
-        <v>6860460</v>
+        <v>6860417</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129073710</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129074043</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>129073070</v>
       </c>
       <c r="B7" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129074896</v>
+        <v>129073823</v>
       </c>
       <c r="B8" t="n">
-        <v>79658</v>
+        <v>78796</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,21 +1305,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469691</v>
+        <v>469769</v>
       </c>
       <c r="R8" t="n">
-        <v>6860502</v>
+        <v>6860351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129073823</v>
+        <v>129074896</v>
       </c>
       <c r="B9" t="n">
-        <v>78796</v>
+        <v>79658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,21 +1402,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469769</v>
+        <v>469691</v>
       </c>
       <c r="R9" t="n">
-        <v>6860351</v>
+        <v>6860502</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1978,54 +1978,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129073789</v>
+        <v>129072852</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>78797</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469761</v>
+        <v>469681</v>
       </c>
       <c r="R15" t="n">
-        <v>6860341</v>
+        <v>6860335</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2084,45 +2075,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129072852</v>
+        <v>129073789</v>
       </c>
       <c r="B16" t="n">
-        <v>78797</v>
+        <v>98676</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469681</v>
+        <v>469761</v>
       </c>
       <c r="R16" t="n">
-        <v>6860335</v>
+        <v>6860341</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2666,54 +2666,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129074106</v>
+        <v>129073686</v>
       </c>
       <c r="B22" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469787</v>
+        <v>469742</v>
       </c>
       <c r="R22" t="n">
-        <v>6860379</v>
+        <v>6860327</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,6 +2737,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2772,45 +2768,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129073686</v>
+        <v>129074106</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469742</v>
+        <v>469787</v>
       </c>
       <c r="R23" t="n">
-        <v>6860327</v>
+        <v>6860379</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,11 +2848,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3168,7 +3168,7 @@
         <v>129240619</v>
       </c>
       <c r="B27" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129240501</v>
+        <v>129240256</v>
       </c>
       <c r="B28" t="n">
-        <v>78797</v>
+        <v>79658</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3282,21 +3282,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469685</v>
+        <v>469555</v>
       </c>
       <c r="R28" t="n">
-        <v>6860410</v>
+        <v>6860433</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129240256</v>
+        <v>129240501</v>
       </c>
       <c r="B29" t="n">
-        <v>79658</v>
+        <v>78797</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469555</v>
+        <v>469685</v>
       </c>
       <c r="R29" t="n">
-        <v>6860433</v>
+        <v>6860410</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
         <v>129242930</v>
       </c>
       <c r="B34" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129073710</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129076566</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129074043</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>129073324</v>
       </c>
       <c r="B5" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>129074721</v>
       </c>
       <c r="B6" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>129073070</v>
       </c>
       <c r="B7" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>129073823</v>
       </c>
       <c r="B8" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>129074896</v>
       </c>
       <c r="B9" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129076255</v>
+        <v>129075167</v>
       </c>
       <c r="B10" t="n">
-        <v>78705</v>
+        <v>78799</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,21 +1499,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469608</v>
+        <v>469625</v>
       </c>
       <c r="R10" t="n">
-        <v>6860373</v>
+        <v>6860490</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129075167</v>
+        <v>129076255</v>
       </c>
       <c r="B11" t="n">
-        <v>78797</v>
+        <v>78707</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469625</v>
+        <v>469608</v>
       </c>
       <c r="R11" t="n">
-        <v>6860490</v>
+        <v>6860373</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129074218</v>
+        <v>129075209</v>
       </c>
       <c r="B12" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469807</v>
+        <v>469625</v>
       </c>
       <c r="R12" t="n">
-        <v>6860393</v>
+        <v>6860485</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129075209</v>
+        <v>129074218</v>
       </c>
       <c r="B13" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469625</v>
+        <v>469807</v>
       </c>
       <c r="R13" t="n">
-        <v>6860485</v>
+        <v>6860393</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
         <v>129075376</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,45 +1978,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129072852</v>
+        <v>129073789</v>
       </c>
       <c r="B15" t="n">
-        <v>78797</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469681</v>
+        <v>469761</v>
       </c>
       <c r="R15" t="n">
-        <v>6860335</v>
+        <v>6860341</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2075,54 +2084,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129073789</v>
+        <v>129072852</v>
       </c>
       <c r="B16" t="n">
-        <v>98676</v>
+        <v>78799</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469761</v>
+        <v>469681</v>
       </c>
       <c r="R16" t="n">
-        <v>6860341</v>
+        <v>6860335</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2184,7 +2184,7 @@
         <v>129074684</v>
       </c>
       <c r="B17" t="n">
-        <v>80172</v>
+        <v>80174</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>129074551</v>
       </c>
       <c r="B18" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>129074540</v>
       </c>
       <c r="B19" t="n">
-        <v>78047</v>
+        <v>78049</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129074919</v>
       </c>
       <c r="B20" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>129075085</v>
       </c>
       <c r="B21" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>129073686</v>
       </c>
       <c r="B22" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>129074106</v>
       </c>
       <c r="B23" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>129075590</v>
       </c>
       <c r="B24" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>129072966</v>
       </c>
       <c r="B25" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>129240565</v>
       </c>
       <c r="B26" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>129240619</v>
       </c>
       <c r="B27" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129240256</v>
       </c>
       <c r="B28" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>129240501</v>
       </c>
       <c r="B29" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>129240555</v>
       </c>
       <c r="B30" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>129240241</v>
       </c>
       <c r="B31" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>129240472</v>
       </c>
       <c r="B32" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>129240219</v>
       </c>
       <c r="B33" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>129242930</v>
       </c>
       <c r="B34" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>129243036</v>
       </c>
       <c r="B35" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>129240407</v>
       </c>
       <c r="B36" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -1294,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129073823</v>
+        <v>129074896</v>
       </c>
       <c r="B8" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,21 +1305,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469769</v>
+        <v>469691</v>
       </c>
       <c r="R8" t="n">
-        <v>6860351</v>
+        <v>6860502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129074896</v>
+        <v>129073823</v>
       </c>
       <c r="B9" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,21 +1402,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469691</v>
+        <v>469769</v>
       </c>
       <c r="R9" t="n">
-        <v>6860502</v>
+        <v>6860351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129075167</v>
+        <v>129076255</v>
       </c>
       <c r="B10" t="n">
-        <v>78799</v>
+        <v>78707</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,21 +1499,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469625</v>
+        <v>469608</v>
       </c>
       <c r="R10" t="n">
-        <v>6860490</v>
+        <v>6860373</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129076255</v>
+        <v>129075167</v>
       </c>
       <c r="B11" t="n">
-        <v>78707</v>
+        <v>78799</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469608</v>
+        <v>469625</v>
       </c>
       <c r="R11" t="n">
-        <v>6860373</v>
+        <v>6860490</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129075209</v>
+        <v>129074218</v>
       </c>
       <c r="B12" t="n">
         <v>78707</v>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469625</v>
+        <v>469807</v>
       </c>
       <c r="R12" t="n">
-        <v>6860485</v>
+        <v>6860393</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,7 +1779,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129074218</v>
+        <v>129075209</v>
       </c>
       <c r="B13" t="n">
         <v>78707</v>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469807</v>
+        <v>469625</v>
       </c>
       <c r="R13" t="n">
-        <v>6860393</v>
+        <v>6860485</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,54 +1978,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129073789</v>
+        <v>129072852</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>78799</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469761</v>
+        <v>469681</v>
       </c>
       <c r="R15" t="n">
-        <v>6860341</v>
+        <v>6860335</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2084,45 +2075,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129072852</v>
+        <v>129073789</v>
       </c>
       <c r="B16" t="n">
-        <v>78799</v>
+        <v>98678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469681</v>
+        <v>469761</v>
       </c>
       <c r="R16" t="n">
-        <v>6860335</v>
+        <v>6860341</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129074540</v>
+        <v>129074919</v>
       </c>
       <c r="B19" t="n">
-        <v>78049</v>
+        <v>78799</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2386,21 +2386,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469743</v>
+        <v>469680</v>
       </c>
       <c r="R19" t="n">
-        <v>6860415</v>
+        <v>6860506</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129074919</v>
+        <v>129074540</v>
       </c>
       <c r="B20" t="n">
-        <v>78799</v>
+        <v>78049</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469680</v>
+        <v>469743</v>
       </c>
       <c r="R20" t="n">
-        <v>6860506</v>
+        <v>6860415</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,45 +2666,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129073686</v>
+        <v>129074106</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469742</v>
+        <v>469787</v>
       </c>
       <c r="R22" t="n">
-        <v>6860327</v>
+        <v>6860379</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,11 +2746,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2768,54 +2772,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129074106</v>
+        <v>129073686</v>
       </c>
       <c r="B23" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469787</v>
+        <v>469742</v>
       </c>
       <c r="R23" t="n">
-        <v>6860379</v>
+        <v>6860327</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,6 +2843,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -1294,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129074896</v>
+        <v>129073823</v>
       </c>
       <c r="B8" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,21 +1305,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469691</v>
+        <v>469769</v>
       </c>
       <c r="R8" t="n">
-        <v>6860502</v>
+        <v>6860351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129073823</v>
+        <v>129074896</v>
       </c>
       <c r="B9" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,21 +1402,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469769</v>
+        <v>469691</v>
       </c>
       <c r="R9" t="n">
-        <v>6860351</v>
+        <v>6860502</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129074218</v>
+        <v>129075209</v>
       </c>
       <c r="B12" t="n">
         <v>78707</v>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469807</v>
+        <v>469625</v>
       </c>
       <c r="R12" t="n">
-        <v>6860393</v>
+        <v>6860485</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,7 +1779,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129075209</v>
+        <v>129074218</v>
       </c>
       <c r="B13" t="n">
         <v>78707</v>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469625</v>
+        <v>469807</v>
       </c>
       <c r="R13" t="n">
-        <v>6860485</v>
+        <v>6860393</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,45 +1876,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129075376</v>
+        <v>129073789</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469623</v>
+        <v>469761</v>
       </c>
       <c r="R14" t="n">
-        <v>6860454</v>
+        <v>6860341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,11 +1956,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,54 +2079,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129073789</v>
+        <v>129075376</v>
       </c>
       <c r="B16" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469761</v>
+        <v>469623</v>
       </c>
       <c r="R16" t="n">
-        <v>6860341</v>
+        <v>6860454</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,6 +2150,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,10 +2375,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129074919</v>
+        <v>129074540</v>
       </c>
       <c r="B19" t="n">
-        <v>78799</v>
+        <v>78049</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2386,21 +2386,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469680</v>
+        <v>469743</v>
       </c>
       <c r="R19" t="n">
-        <v>6860506</v>
+        <v>6860415</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129074540</v>
+        <v>129074919</v>
       </c>
       <c r="B20" t="n">
-        <v>78049</v>
+        <v>78799</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469743</v>
+        <v>469680</v>
       </c>
       <c r="R20" t="n">
-        <v>6860415</v>
+        <v>6860506</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129240256</v>
+        <v>129240501</v>
       </c>
       <c r="B28" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3282,21 +3282,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469555</v>
+        <v>469685</v>
       </c>
       <c r="R28" t="n">
-        <v>6860433</v>
+        <v>6860410</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129240501</v>
+        <v>129240256</v>
       </c>
       <c r="B29" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469685</v>
+        <v>469555</v>
       </c>
       <c r="R29" t="n">
-        <v>6860410</v>
+        <v>6860433</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129073710</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,45 +781,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129076566</v>
+        <v>129074043</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469689</v>
+        <v>469786</v>
       </c>
       <c r="R3" t="n">
-        <v>6860378</v>
+        <v>6860361</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,54 +887,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129074043</v>
+        <v>129076566</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469786</v>
+        <v>469689</v>
       </c>
       <c r="R4" t="n">
-        <v>6860361</v>
+        <v>6860378</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +958,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1186,7 +1186,7 @@
         <v>129073070</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129073823</v>
+        <v>129074896</v>
       </c>
       <c r="B8" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,21 +1305,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469769</v>
+        <v>469691</v>
       </c>
       <c r="R8" t="n">
-        <v>6860351</v>
+        <v>6860502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129074896</v>
+        <v>129073823</v>
       </c>
       <c r="B9" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,21 +1402,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469691</v>
+        <v>469769</v>
       </c>
       <c r="R9" t="n">
-        <v>6860502</v>
+        <v>6860351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1876,54 +1876,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129073789</v>
+        <v>129075376</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469761</v>
+        <v>469623</v>
       </c>
       <c r="R14" t="n">
-        <v>6860341</v>
+        <v>6860454</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,6 +1947,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,45 +2075,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129075376</v>
+        <v>129073789</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469623</v>
+        <v>469761</v>
       </c>
       <c r="R16" t="n">
-        <v>6860454</v>
+        <v>6860341</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,11 +2155,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,10 +2375,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129074540</v>
+        <v>129074919</v>
       </c>
       <c r="B19" t="n">
-        <v>78049</v>
+        <v>78799</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2386,21 +2386,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469743</v>
+        <v>469680</v>
       </c>
       <c r="R19" t="n">
-        <v>6860415</v>
+        <v>6860506</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129074919</v>
+        <v>129074540</v>
       </c>
       <c r="B20" t="n">
-        <v>78799</v>
+        <v>78049</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469680</v>
+        <v>469743</v>
       </c>
       <c r="R20" t="n">
-        <v>6860506</v>
+        <v>6860415</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,54 +2666,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129074106</v>
+        <v>129073686</v>
       </c>
       <c r="B22" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469787</v>
+        <v>469742</v>
       </c>
       <c r="R22" t="n">
-        <v>6860379</v>
+        <v>6860327</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,6 +2737,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2772,45 +2768,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129073686</v>
+        <v>129074106</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469742</v>
+        <v>469787</v>
       </c>
       <c r="R23" t="n">
-        <v>6860327</v>
+        <v>6860379</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,11 +2848,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3168,7 +3168,7 @@
         <v>129240619</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129240501</v>
+        <v>129240256</v>
       </c>
       <c r="B28" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3282,21 +3282,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469685</v>
+        <v>469555</v>
       </c>
       <c r="R28" t="n">
-        <v>6860410</v>
+        <v>6860433</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129240256</v>
+        <v>129240501</v>
       </c>
       <c r="B29" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469555</v>
+        <v>469685</v>
       </c>
       <c r="R29" t="n">
-        <v>6860433</v>
+        <v>6860410</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129073710</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,54 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129074043</v>
+        <v>129076566</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469786</v>
+        <v>469689</v>
       </c>
       <c r="R3" t="n">
-        <v>6860361</v>
+        <v>6860378</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,6 +852,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,45 +883,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129076566</v>
+        <v>129074043</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469689</v>
+        <v>469786</v>
       </c>
       <c r="R4" t="n">
-        <v>6860378</v>
+        <v>6860361</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1186,7 +1186,7 @@
         <v>129073070</v>
       </c>
       <c r="B7" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>129073789</v>
       </c>
       <c r="B16" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129074919</v>
+        <v>129074540</v>
       </c>
       <c r="B19" t="n">
-        <v>78799</v>
+        <v>78049</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2386,21 +2386,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469680</v>
+        <v>469743</v>
       </c>
       <c r="R19" t="n">
-        <v>6860506</v>
+        <v>6860415</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129074540</v>
+        <v>129074919</v>
       </c>
       <c r="B20" t="n">
-        <v>78049</v>
+        <v>78799</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469743</v>
+        <v>469680</v>
       </c>
       <c r="R20" t="n">
-        <v>6860415</v>
+        <v>6860506</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,45 +2666,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129073686</v>
+        <v>129074106</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469742</v>
+        <v>469787</v>
       </c>
       <c r="R22" t="n">
-        <v>6860327</v>
+        <v>6860379</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,11 +2746,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2768,54 +2772,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129074106</v>
+        <v>129073686</v>
       </c>
       <c r="B23" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469787</v>
+        <v>469742</v>
       </c>
       <c r="R23" t="n">
-        <v>6860379</v>
+        <v>6860327</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,6 +2843,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3168,7 +3168,7 @@
         <v>129240619</v>
       </c>
       <c r="B27" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129073710</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129074043</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1876,45 +1876,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129075376</v>
+        <v>129073789</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469623</v>
+        <v>469761</v>
       </c>
       <c r="R14" t="n">
-        <v>6860454</v>
+        <v>6860341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,11 +1956,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1978,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129072852</v>
+        <v>129075376</v>
       </c>
       <c r="B15" t="n">
-        <v>78799</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1989,34 +1993,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469681</v>
+        <v>469623</v>
       </c>
       <c r="R15" t="n">
-        <v>6860335</v>
+        <v>6860454</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,6 +2053,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2075,54 +2084,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129073789</v>
+        <v>129072852</v>
       </c>
       <c r="B16" t="n">
-        <v>98705</v>
+        <v>78799</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469761</v>
+        <v>469681</v>
       </c>
       <c r="R16" t="n">
-        <v>6860341</v>
+        <v>6860335</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2666,54 +2666,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129074106</v>
+        <v>129073686</v>
       </c>
       <c r="B22" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469787</v>
+        <v>469742</v>
       </c>
       <c r="R22" t="n">
-        <v>6860379</v>
+        <v>6860327</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,6 +2737,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2772,45 +2768,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129073686</v>
+        <v>129074106</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469742</v>
+        <v>469787</v>
       </c>
       <c r="R23" t="n">
-        <v>6860327</v>
+        <v>6860379</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,11 +2848,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3168,7 +3168,7 @@
         <v>129240619</v>
       </c>
       <c r="B27" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129073710</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129074043</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>129073324</v>
       </c>
       <c r="B5" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>129074721</v>
       </c>
       <c r="B6" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,59 +1183,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129073070</v>
+        <v>129074896</v>
       </c>
       <c r="B7" t="n">
-        <v>92822</v>
+        <v>79662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469736</v>
+        <v>469691</v>
       </c>
       <c r="R7" t="n">
-        <v>6860324</v>
+        <v>6860502</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,10 +1280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129074896</v>
+        <v>129073823</v>
       </c>
       <c r="B8" t="n">
-        <v>79660</v>
+        <v>78800</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,21 +1291,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1329,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469691</v>
+        <v>469769</v>
       </c>
       <c r="R8" t="n">
-        <v>6860502</v>
+        <v>6860351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,45 +1377,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129073823</v>
+        <v>129073070</v>
       </c>
       <c r="B9" t="n">
-        <v>78798</v>
+        <v>92825</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469769</v>
+        <v>469736</v>
       </c>
       <c r="R9" t="n">
-        <v>6860351</v>
+        <v>6860324</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
         <v>129076255</v>
       </c>
       <c r="B10" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>129075167</v>
       </c>
       <c r="B11" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129075209</v>
+        <v>129074218</v>
       </c>
       <c r="B12" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469625</v>
+        <v>469807</v>
       </c>
       <c r="R12" t="n">
-        <v>6860485</v>
+        <v>6860393</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129074218</v>
+        <v>129075209</v>
       </c>
       <c r="B13" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469807</v>
+        <v>469625</v>
       </c>
       <c r="R13" t="n">
-        <v>6860393</v>
+        <v>6860485</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
         <v>129073789</v>
       </c>
       <c r="B14" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129075376</v>
+        <v>129072852</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>78801</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,34 +1993,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469623</v>
+        <v>469681</v>
       </c>
       <c r="R15" t="n">
-        <v>6860454</v>
+        <v>6860335</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,11 +2053,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2084,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129072852</v>
+        <v>129075376</v>
       </c>
       <c r="B16" t="n">
-        <v>78799</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2095,34 +2090,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469681</v>
+        <v>469623</v>
       </c>
       <c r="R16" t="n">
-        <v>6860335</v>
+        <v>6860454</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,6 +2150,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2184,7 +2184,7 @@
         <v>129074684</v>
       </c>
       <c r="B17" t="n">
-        <v>80174</v>
+        <v>80176</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>129074551</v>
       </c>
       <c r="B18" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>129074540</v>
       </c>
       <c r="B19" t="n">
-        <v>78049</v>
+        <v>78051</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129074919</v>
       </c>
       <c r="B20" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>129075085</v>
       </c>
       <c r="B21" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>129074106</v>
       </c>
       <c r="B23" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>129075590</v>
       </c>
       <c r="B24" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>129072966</v>
       </c>
       <c r="B25" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>129240565</v>
       </c>
       <c r="B26" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>129240619</v>
       </c>
       <c r="B27" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129240256</v>
       </c>
       <c r="B28" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>129240501</v>
       </c>
       <c r="B29" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>129240555</v>
       </c>
       <c r="B30" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>129240241</v>
       </c>
       <c r="B31" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>129240472</v>
       </c>
       <c r="B32" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>129240219</v>
       </c>
       <c r="B33" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>129242930</v>
       </c>
       <c r="B34" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>129240407</v>
       </c>
       <c r="B36" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -1183,45 +1183,59 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129074896</v>
+        <v>129073070</v>
       </c>
       <c r="B7" t="n">
-        <v>79662</v>
+        <v>92825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469691</v>
+        <v>469736</v>
       </c>
       <c r="R7" t="n">
-        <v>6860502</v>
+        <v>6860324</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129073823</v>
+        <v>129074896</v>
       </c>
       <c r="B8" t="n">
-        <v>78800</v>
+        <v>79662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,21 +1305,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469769</v>
+        <v>469691</v>
       </c>
       <c r="R8" t="n">
-        <v>6860351</v>
+        <v>6860502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,59 +1391,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129073070</v>
+        <v>129073823</v>
       </c>
       <c r="B9" t="n">
-        <v>92825</v>
+        <v>78800</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469736</v>
+        <v>469769</v>
       </c>
       <c r="R9" t="n">
-        <v>6860324</v>
+        <v>6860351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129073710</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,45 +781,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129076566</v>
+        <v>129074043</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469689</v>
+        <v>469786</v>
       </c>
       <c r="R3" t="n">
-        <v>6860378</v>
+        <v>6860361</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,54 +887,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129074043</v>
+        <v>129076566</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469786</v>
+        <v>469689</v>
       </c>
       <c r="R4" t="n">
-        <v>6860361</v>
+        <v>6860378</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +958,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,7 +992,7 @@
         <v>129073324</v>
       </c>
       <c r="B5" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>129074721</v>
       </c>
       <c r="B6" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>129073070</v>
       </c>
       <c r="B7" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129074896</v>
+        <v>129073823</v>
       </c>
       <c r="B8" t="n">
-        <v>79662</v>
+        <v>78801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,21 +1305,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469691</v>
+        <v>469769</v>
       </c>
       <c r="R8" t="n">
-        <v>6860502</v>
+        <v>6860351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129073823</v>
+        <v>129074896</v>
       </c>
       <c r="B9" t="n">
-        <v>78800</v>
+        <v>79663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,21 +1402,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469769</v>
+        <v>469691</v>
       </c>
       <c r="R9" t="n">
-        <v>6860351</v>
+        <v>6860502</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
         <v>129076255</v>
       </c>
       <c r="B10" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>129075167</v>
       </c>
       <c r="B11" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129074218</v>
+        <v>129075209</v>
       </c>
       <c r="B12" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469807</v>
+        <v>469625</v>
       </c>
       <c r="R12" t="n">
-        <v>6860393</v>
+        <v>6860485</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129075209</v>
+        <v>129074218</v>
       </c>
       <c r="B13" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469625</v>
+        <v>469807</v>
       </c>
       <c r="R13" t="n">
-        <v>6860485</v>
+        <v>6860393</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,54 +1876,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129073789</v>
+        <v>129075376</v>
       </c>
       <c r="B14" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469761</v>
+        <v>469623</v>
       </c>
       <c r="R14" t="n">
-        <v>6860341</v>
+        <v>6860454</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,6 +1947,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1982,45 +1978,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129072852</v>
+        <v>129073789</v>
       </c>
       <c r="B15" t="n">
-        <v>78801</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469681</v>
+        <v>469761</v>
       </c>
       <c r="R15" t="n">
-        <v>6860335</v>
+        <v>6860341</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,10 +2084,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129075376</v>
+        <v>129072852</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,34 +2095,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469623</v>
+        <v>469681</v>
       </c>
       <c r="R16" t="n">
-        <v>6860454</v>
+        <v>6860335</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,11 +2155,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2181,32 +2181,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129074684</v>
+        <v>129074551</v>
       </c>
       <c r="B17" t="n">
-        <v>80176</v>
+        <v>79634</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>469714</v>
+        <v>469743</v>
       </c>
       <c r="R17" t="n">
-        <v>6860460</v>
+        <v>6860417</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,32 +2278,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129074551</v>
+        <v>129074684</v>
       </c>
       <c r="B18" t="n">
-        <v>79633</v>
+        <v>80177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469743</v>
+        <v>469714</v>
       </c>
       <c r="R18" t="n">
-        <v>6860417</v>
+        <v>6860460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2378,7 +2378,7 @@
         <v>129074540</v>
       </c>
       <c r="B19" t="n">
-        <v>78051</v>
+        <v>78052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129074919</v>
       </c>
       <c r="B20" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>129075085</v>
       </c>
       <c r="B21" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,45 +2666,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129073686</v>
+        <v>129074106</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469742</v>
+        <v>469787</v>
       </c>
       <c r="R22" t="n">
-        <v>6860327</v>
+        <v>6860379</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,11 +2746,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2768,54 +2772,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129074106</v>
+        <v>129073686</v>
       </c>
       <c r="B23" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469787</v>
+        <v>469742</v>
       </c>
       <c r="R23" t="n">
-        <v>6860379</v>
+        <v>6860327</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,6 +2843,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2877,7 +2877,7 @@
         <v>129075590</v>
       </c>
       <c r="B24" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>129072966</v>
       </c>
       <c r="B25" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>129240565</v>
       </c>
       <c r="B26" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>129240619</v>
       </c>
       <c r="B27" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129240256</v>
       </c>
       <c r="B28" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>129240501</v>
       </c>
       <c r="B29" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>129240555</v>
       </c>
       <c r="B30" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>129240241</v>
       </c>
       <c r="B31" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>129240472</v>
       </c>
       <c r="B32" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>129240219</v>
       </c>
       <c r="B33" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>129242930</v>
       </c>
       <c r="B34" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>129240407</v>
       </c>
       <c r="B36" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129073710</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,54 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129074043</v>
+        <v>129076566</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469786</v>
+        <v>469689</v>
       </c>
       <c r="R3" t="n">
-        <v>6860361</v>
+        <v>6860378</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,6 +852,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,45 +883,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129076566</v>
+        <v>129074043</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469689</v>
+        <v>469786</v>
       </c>
       <c r="R4" t="n">
-        <v>6860378</v>
+        <v>6860361</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1186,7 +1186,7 @@
         <v>129073070</v>
       </c>
       <c r="B7" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129073823</v>
+        <v>129074896</v>
       </c>
       <c r="B8" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,21 +1305,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469769</v>
+        <v>469691</v>
       </c>
       <c r="R8" t="n">
-        <v>6860351</v>
+        <v>6860502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129074896</v>
+        <v>129073823</v>
       </c>
       <c r="B9" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,21 +1402,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469691</v>
+        <v>469769</v>
       </c>
       <c r="R9" t="n">
-        <v>6860502</v>
+        <v>6860351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129075209</v>
+        <v>129074218</v>
       </c>
       <c r="B12" t="n">
         <v>78710</v>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469625</v>
+        <v>469807</v>
       </c>
       <c r="R12" t="n">
-        <v>6860485</v>
+        <v>6860393</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,7 +1779,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129074218</v>
+        <v>129075209</v>
       </c>
       <c r="B13" t="n">
         <v>78710</v>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469807</v>
+        <v>469625</v>
       </c>
       <c r="R13" t="n">
-        <v>6860393</v>
+        <v>6860485</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,7 +1981,7 @@
         <v>129073789</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,32 +2181,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129074551</v>
+        <v>129074684</v>
       </c>
       <c r="B17" t="n">
-        <v>79634</v>
+        <v>80177</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>469743</v>
+        <v>469714</v>
       </c>
       <c r="R17" t="n">
-        <v>6860417</v>
+        <v>6860460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,32 +2278,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129074684</v>
+        <v>129074551</v>
       </c>
       <c r="B18" t="n">
-        <v>80177</v>
+        <v>79634</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6461</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469714</v>
+        <v>469743</v>
       </c>
       <c r="R18" t="n">
-        <v>6860460</v>
+        <v>6860417</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2666,54 +2666,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129074106</v>
+        <v>129073686</v>
       </c>
       <c r="B22" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469787</v>
+        <v>469742</v>
       </c>
       <c r="R22" t="n">
-        <v>6860379</v>
+        <v>6860327</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,6 +2737,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2772,45 +2768,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129073686</v>
+        <v>129074106</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469742</v>
+        <v>469787</v>
       </c>
       <c r="R23" t="n">
-        <v>6860327</v>
+        <v>6860379</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,11 +2848,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3168,7 +3168,7 @@
         <v>129240619</v>
       </c>
       <c r="B27" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129073710</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129074043</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>129073070</v>
       </c>
       <c r="B7" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129074218</v>
+        <v>129075209</v>
       </c>
       <c r="B12" t="n">
         <v>78710</v>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469807</v>
+        <v>469625</v>
       </c>
       <c r="R12" t="n">
-        <v>6860393</v>
+        <v>6860485</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,7 +1779,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129075209</v>
+        <v>129074218</v>
       </c>
       <c r="B13" t="n">
         <v>78710</v>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469625</v>
+        <v>469807</v>
       </c>
       <c r="R13" t="n">
-        <v>6860485</v>
+        <v>6860393</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129075376</v>
+        <v>129072852</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,34 +1887,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469623</v>
+        <v>469681</v>
       </c>
       <c r="R14" t="n">
-        <v>6860454</v>
+        <v>6860335</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,11 +1947,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1978,54 +1973,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129073789</v>
+        <v>129075376</v>
       </c>
       <c r="B15" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469761</v>
+        <v>469623</v>
       </c>
       <c r="R15" t="n">
-        <v>6860341</v>
+        <v>6860454</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2058,6 +2044,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2084,45 +2075,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129072852</v>
+        <v>129073789</v>
       </c>
       <c r="B16" t="n">
-        <v>78802</v>
+        <v>98724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469681</v>
+        <v>469761</v>
       </c>
       <c r="R16" t="n">
-        <v>6860335</v>
+        <v>6860341</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2666,45 +2666,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129073686</v>
+        <v>129074106</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469742</v>
+        <v>469787</v>
       </c>
       <c r="R22" t="n">
-        <v>6860327</v>
+        <v>6860379</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,11 +2746,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2768,54 +2772,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129074106</v>
+        <v>129073686</v>
       </c>
       <c r="B23" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469787</v>
+        <v>469742</v>
       </c>
       <c r="R23" t="n">
-        <v>6860379</v>
+        <v>6860327</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,6 +2843,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3168,7 +3168,7 @@
         <v>129240619</v>
       </c>
       <c r="B27" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -1183,59 +1183,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129073070</v>
+        <v>129073823</v>
       </c>
       <c r="B7" t="n">
-        <v>92832</v>
+        <v>78801</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469736</v>
+        <v>469769</v>
       </c>
       <c r="R7" t="n">
-        <v>6860324</v>
+        <v>6860351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1391,45 +1377,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129073823</v>
+        <v>129073070</v>
       </c>
       <c r="B9" t="n">
-        <v>78801</v>
+        <v>92832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469769</v>
+        <v>469736</v>
       </c>
       <c r="R9" t="n">
-        <v>6860351</v>
+        <v>6860324</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129072852</v>
+        <v>129075376</v>
       </c>
       <c r="B14" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,34 +1887,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469681</v>
+        <v>469623</v>
       </c>
       <c r="R14" t="n">
-        <v>6860335</v>
+        <v>6860454</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,6 +1947,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1973,45 +1978,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129075376</v>
+        <v>129073789</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469623</v>
+        <v>469761</v>
       </c>
       <c r="R15" t="n">
-        <v>6860454</v>
+        <v>6860341</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2044,11 +2058,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2075,54 +2084,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129073789</v>
+        <v>129072852</v>
       </c>
       <c r="B16" t="n">
-        <v>98724</v>
+        <v>78802</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469761</v>
+        <v>469681</v>
       </c>
       <c r="R16" t="n">
-        <v>6860341</v>
+        <v>6860335</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129074540</v>
+        <v>129074919</v>
       </c>
       <c r="B19" t="n">
-        <v>78052</v>
+        <v>78802</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2386,21 +2386,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469743</v>
+        <v>469680</v>
       </c>
       <c r="R19" t="n">
-        <v>6860415</v>
+        <v>6860506</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129074919</v>
+        <v>129074540</v>
       </c>
       <c r="B20" t="n">
-        <v>78802</v>
+        <v>78052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469680</v>
+        <v>469743</v>
       </c>
       <c r="R20" t="n">
-        <v>6860506</v>
+        <v>6860415</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,54 +2666,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129074106</v>
+        <v>129073686</v>
       </c>
       <c r="B22" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469787</v>
+        <v>469742</v>
       </c>
       <c r="R22" t="n">
-        <v>6860379</v>
+        <v>6860327</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,6 +2737,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2772,45 +2768,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129073686</v>
+        <v>129074106</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469742</v>
+        <v>469787</v>
       </c>
       <c r="R23" t="n">
-        <v>6860327</v>
+        <v>6860379</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,11 +2848,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3271,10 +3271,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129240256</v>
+        <v>129240501</v>
       </c>
       <c r="B28" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3282,21 +3282,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469555</v>
+        <v>469685</v>
       </c>
       <c r="R28" t="n">
-        <v>6860433</v>
+        <v>6860410</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129240501</v>
+        <v>129240256</v>
       </c>
       <c r="B29" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469685</v>
+        <v>469555</v>
       </c>
       <c r="R29" t="n">
-        <v>6860410</v>
+        <v>6860433</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -1488,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129076255</v>
+        <v>129075167</v>
       </c>
       <c r="B10" t="n">
-        <v>78710</v>
+        <v>78802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,21 +1499,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469608</v>
+        <v>469625</v>
       </c>
       <c r="R10" t="n">
-        <v>6860373</v>
+        <v>6860490</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129075167</v>
+        <v>129076255</v>
       </c>
       <c r="B11" t="n">
-        <v>78802</v>
+        <v>78710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469625</v>
+        <v>469608</v>
       </c>
       <c r="R11" t="n">
-        <v>6860490</v>
+        <v>6860373</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129074919</v>
+        <v>129074540</v>
       </c>
       <c r="B19" t="n">
-        <v>78802</v>
+        <v>78052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2386,21 +2386,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469680</v>
+        <v>469743</v>
       </c>
       <c r="R19" t="n">
-        <v>6860506</v>
+        <v>6860415</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129074540</v>
+        <v>129074919</v>
       </c>
       <c r="B20" t="n">
-        <v>78052</v>
+        <v>78802</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469743</v>
+        <v>469680</v>
       </c>
       <c r="R20" t="n">
-        <v>6860415</v>
+        <v>6860506</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129240501</v>
+        <v>129240256</v>
       </c>
       <c r="B28" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3282,21 +3282,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469685</v>
+        <v>469555</v>
       </c>
       <c r="R28" t="n">
-        <v>6860410</v>
+        <v>6860433</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129240256</v>
+        <v>129240501</v>
       </c>
       <c r="B29" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469555</v>
+        <v>469685</v>
       </c>
       <c r="R29" t="n">
-        <v>6860433</v>
+        <v>6860410</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129073710</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129074043</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1183,45 +1183,59 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129073823</v>
+        <v>129073070</v>
       </c>
       <c r="B7" t="n">
-        <v>78801</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469769</v>
+        <v>469736</v>
       </c>
       <c r="R7" t="n">
-        <v>6860351</v>
+        <v>6860324</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,59 +1391,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129073070</v>
+        <v>129073823</v>
       </c>
       <c r="B9" t="n">
-        <v>92832</v>
+        <v>78801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469736</v>
+        <v>469769</v>
       </c>
       <c r="R9" t="n">
-        <v>6860324</v>
+        <v>6860351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1876,45 +1876,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129075376</v>
+        <v>129073789</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469623</v>
+        <v>469761</v>
       </c>
       <c r="R14" t="n">
-        <v>6860454</v>
+        <v>6860341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,11 +1956,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1978,54 +1982,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129073789</v>
+        <v>129075376</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469761</v>
+        <v>469623</v>
       </c>
       <c r="R15" t="n">
-        <v>6860341</v>
+        <v>6860454</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2058,6 +2053,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2771,7 +2771,7 @@
         <v>129074106</v>
       </c>
       <c r="B23" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>129240619</v>
       </c>
       <c r="B27" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -781,45 +781,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129076566</v>
+        <v>129074043</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469689</v>
+        <v>469786</v>
       </c>
       <c r="R3" t="n">
-        <v>6860378</v>
+        <v>6860361</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,54 +887,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129074043</v>
+        <v>129076566</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469786</v>
+        <v>469689</v>
       </c>
       <c r="R4" t="n">
-        <v>6860361</v>
+        <v>6860378</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +958,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129075376</v>
+        <v>129072852</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,34 +1993,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469623</v>
+        <v>469681</v>
       </c>
       <c r="R15" t="n">
-        <v>6860454</v>
+        <v>6860335</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,11 +2053,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2084,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129072852</v>
+        <v>129075376</v>
       </c>
       <c r="B16" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2095,34 +2090,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469681</v>
+        <v>469623</v>
       </c>
       <c r="R16" t="n">
-        <v>6860335</v>
+        <v>6860454</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,6 +2150,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,10 +2375,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129074540</v>
+        <v>129074919</v>
       </c>
       <c r="B19" t="n">
-        <v>78052</v>
+        <v>78802</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2386,21 +2386,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469743</v>
+        <v>469680</v>
       </c>
       <c r="R19" t="n">
-        <v>6860415</v>
+        <v>6860506</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129074919</v>
+        <v>129074540</v>
       </c>
       <c r="B20" t="n">
-        <v>78802</v>
+        <v>78052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469680</v>
+        <v>469743</v>
       </c>
       <c r="R20" t="n">
-        <v>6860506</v>
+        <v>6860415</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129072852</v>
+        <v>129075376</v>
       </c>
       <c r="B15" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,34 +1993,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469681</v>
+        <v>469623</v>
       </c>
       <c r="R15" t="n">
-        <v>6860335</v>
+        <v>6860454</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,6 +2053,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2079,10 +2084,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129075376</v>
+        <v>129072852</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,34 +2095,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469623</v>
+        <v>469681</v>
       </c>
       <c r="R16" t="n">
-        <v>6860454</v>
+        <v>6860335</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,11 +2155,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2666,45 +2666,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129073686</v>
+        <v>129074106</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469742</v>
+        <v>469787</v>
       </c>
       <c r="R22" t="n">
-        <v>6860327</v>
+        <v>6860379</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,11 +2746,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2768,54 +2772,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129074106</v>
+        <v>129073686</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469787</v>
+        <v>469742</v>
       </c>
       <c r="R23" t="n">
-        <v>6860379</v>
+        <v>6860327</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,6 +2843,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3271,10 +3271,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129240256</v>
+        <v>129240501</v>
       </c>
       <c r="B28" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3282,21 +3282,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469555</v>
+        <v>469685</v>
       </c>
       <c r="R28" t="n">
-        <v>6860433</v>
+        <v>6860410</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129240501</v>
+        <v>129240256</v>
       </c>
       <c r="B29" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469685</v>
+        <v>469555</v>
       </c>
       <c r="R29" t="n">
-        <v>6860410</v>
+        <v>6860433</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -781,54 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129074043</v>
+        <v>129076566</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469786</v>
+        <v>469689</v>
       </c>
       <c r="R3" t="n">
-        <v>6860361</v>
+        <v>6860378</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,6 +852,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,45 +883,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129076566</v>
+        <v>129074043</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469689</v>
+        <v>469786</v>
       </c>
       <c r="R4" t="n">
-        <v>6860378</v>
+        <v>6860361</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1876,54 +1876,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129073789</v>
+        <v>129075376</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469761</v>
+        <v>469623</v>
       </c>
       <c r="R14" t="n">
-        <v>6860341</v>
+        <v>6860454</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,6 +1947,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1982,45 +1978,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129075376</v>
+        <v>129073789</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469623</v>
+        <v>469761</v>
       </c>
       <c r="R15" t="n">
-        <v>6860454</v>
+        <v>6860341</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,11 +2058,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2666,54 +2666,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129074106</v>
+        <v>129073686</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469787</v>
+        <v>469742</v>
       </c>
       <c r="R22" t="n">
-        <v>6860379</v>
+        <v>6860327</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,6 +2737,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2772,45 +2768,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129073686</v>
+        <v>129074106</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469742</v>
+        <v>469787</v>
       </c>
       <c r="R23" t="n">
-        <v>6860327</v>
+        <v>6860379</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,11 +2848,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3271,10 +3271,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129240501</v>
+        <v>129240256</v>
       </c>
       <c r="B28" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3282,21 +3282,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469685</v>
+        <v>469555</v>
       </c>
       <c r="R28" t="n">
-        <v>6860410</v>
+        <v>6860433</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129240256</v>
+        <v>129240501</v>
       </c>
       <c r="B29" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469555</v>
+        <v>469685</v>
       </c>
       <c r="R29" t="n">
-        <v>6860433</v>
+        <v>6860410</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -3271,10 +3271,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129240256</v>
+        <v>129240501</v>
       </c>
       <c r="B28" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3282,21 +3282,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469555</v>
+        <v>469685</v>
       </c>
       <c r="R28" t="n">
-        <v>6860433</v>
+        <v>6860410</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129240501</v>
+        <v>129240256</v>
       </c>
       <c r="B29" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469685</v>
+        <v>469555</v>
       </c>
       <c r="R29" t="n">
-        <v>6860410</v>
+        <v>6860433</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -3271,10 +3271,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129240501</v>
+        <v>129240256</v>
       </c>
       <c r="B28" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3282,21 +3282,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469685</v>
+        <v>469555</v>
       </c>
       <c r="R28" t="n">
-        <v>6860410</v>
+        <v>6860433</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129240256</v>
+        <v>129240501</v>
       </c>
       <c r="B29" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469555</v>
+        <v>469685</v>
       </c>
       <c r="R29" t="n">
-        <v>6860433</v>
+        <v>6860410</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -3071,7 +3071,7 @@
         <v>129240565</v>
       </c>
       <c r="B26" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>129240619</v>
       </c>
       <c r="B27" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129240256</v>
       </c>
       <c r="B28" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>129240501</v>
       </c>
       <c r="B29" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>129240555</v>
       </c>
       <c r="B30" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>129240241</v>
       </c>
       <c r="B31" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>129240472</v>
       </c>
       <c r="B32" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>129240219</v>
       </c>
       <c r="B33" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>129242930</v>
       </c>
       <c r="B34" t="n">
-        <v>83012</v>
+        <v>83039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>129243036</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>129240407</v>
       </c>
       <c r="B36" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -3071,7 +3071,7 @@
         <v>129240565</v>
       </c>
       <c r="B26" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>129240619</v>
       </c>
       <c r="B27" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129240256</v>
+        <v>129240501</v>
       </c>
       <c r="B28" t="n">
-        <v>79689</v>
+        <v>78833</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3282,21 +3282,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469555</v>
+        <v>469685</v>
       </c>
       <c r="R28" t="n">
-        <v>6860433</v>
+        <v>6860410</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129240501</v>
+        <v>129240256</v>
       </c>
       <c r="B29" t="n">
-        <v>78828</v>
+        <v>79694</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469685</v>
+        <v>469555</v>
       </c>
       <c r="R29" t="n">
-        <v>6860410</v>
+        <v>6860433</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3468,7 +3468,7 @@
         <v>129240555</v>
       </c>
       <c r="B30" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>129240241</v>
       </c>
       <c r="B31" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>129240472</v>
       </c>
       <c r="B32" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>129240219</v>
       </c>
       <c r="B33" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>129242930</v>
       </c>
       <c r="B34" t="n">
-        <v>83039</v>
+        <v>83044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>129243036</v>
       </c>
       <c r="B35" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>129240407</v>
       </c>
       <c r="B36" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129073710</v>
+        <v>129076566</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469757</v>
+        <v>469689</v>
       </c>
       <c r="R2" t="n">
-        <v>6860334</v>
+        <v>6860378</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129076566</v>
+        <v>129073324</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469689</v>
+        <v>469745</v>
       </c>
       <c r="R3" t="n">
-        <v>6860378</v>
+        <v>6860335</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,54 +874,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129074043</v>
+        <v>129074721</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>78802</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469786</v>
+        <v>469722</v>
       </c>
       <c r="R4" t="n">
-        <v>6860361</v>
+        <v>6860490</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,45 +971,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129073324</v>
+        <v>129073070</v>
       </c>
       <c r="B5" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469745</v>
+        <v>469736</v>
       </c>
       <c r="R5" t="n">
-        <v>6860335</v>
+        <v>6860324</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,10 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129074721</v>
+        <v>129074896</v>
       </c>
       <c r="B6" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1097,21 +1093,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469722</v>
+        <v>469691</v>
       </c>
       <c r="R6" t="n">
-        <v>6860490</v>
+        <v>6860502</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,59 +1179,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129073070</v>
+        <v>129075167</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469736</v>
+        <v>469625</v>
       </c>
       <c r="R7" t="n">
-        <v>6860324</v>
+        <v>6860490</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,10 +1276,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129074896</v>
+        <v>129076255</v>
       </c>
       <c r="B8" t="n">
-        <v>79663</v>
+        <v>78710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,21 +1287,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1329,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469691</v>
+        <v>469608</v>
       </c>
       <c r="R8" t="n">
-        <v>6860502</v>
+        <v>6860373</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129073823</v>
+        <v>129075209</v>
       </c>
       <c r="B9" t="n">
-        <v>78801</v>
+        <v>78710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469769</v>
+        <v>469625</v>
       </c>
       <c r="R9" t="n">
-        <v>6860351</v>
+        <v>6860485</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,10 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129075167</v>
+        <v>129074218</v>
       </c>
       <c r="B10" t="n">
-        <v>78802</v>
+        <v>78710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,21 +1481,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469625</v>
+        <v>469807</v>
       </c>
       <c r="R10" t="n">
-        <v>6860490</v>
+        <v>6860393</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,10 +1567,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129076255</v>
+        <v>129075376</v>
       </c>
       <c r="B11" t="n">
-        <v>78710</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1578,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469608</v>
+        <v>469623</v>
       </c>
       <c r="R11" t="n">
-        <v>6860373</v>
+        <v>6860454</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1656,6 +1638,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1682,10 +1669,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129075209</v>
+        <v>129072852</v>
       </c>
       <c r="B12" t="n">
-        <v>78710</v>
+        <v>78802</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1693,34 +1680,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469625</v>
+        <v>469681</v>
       </c>
       <c r="R12" t="n">
-        <v>6860485</v>
+        <v>6860335</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,32 +1766,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129074218</v>
+        <v>129074684</v>
       </c>
       <c r="B13" t="n">
-        <v>78710</v>
+        <v>80177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469807</v>
+        <v>469714</v>
       </c>
       <c r="R13" t="n">
-        <v>6860393</v>
+        <v>6860460</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,10 +1863,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129075376</v>
+        <v>129074551</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79634</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,21 +1874,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1911,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469623</v>
+        <v>469743</v>
       </c>
       <c r="R14" t="n">
-        <v>6860454</v>
+        <v>6860417</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,11 +1934,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1978,54 +1960,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129073789</v>
+        <v>129074919</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>78802</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469761</v>
+        <v>469680</v>
       </c>
       <c r="R15" t="n">
-        <v>6860341</v>
+        <v>6860506</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2084,10 +2057,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129072852</v>
+        <v>129074540</v>
       </c>
       <c r="B16" t="n">
-        <v>78802</v>
+        <v>78052</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2095,34 +2068,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469681</v>
+        <v>469743</v>
       </c>
       <c r="R16" t="n">
-        <v>6860335</v>
+        <v>6860415</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2181,32 +2154,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129074684</v>
+        <v>129075085</v>
       </c>
       <c r="B17" t="n">
-        <v>80177</v>
+        <v>78710</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2216,13 +2189,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>469714</v>
+        <v>469663</v>
       </c>
       <c r="R17" t="n">
-        <v>6860460</v>
+        <v>6860504</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2278,10 +2251,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129074551</v>
+        <v>129073686</v>
       </c>
       <c r="B18" t="n">
-        <v>79634</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2289,21 +2262,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2313,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469743</v>
+        <v>469742</v>
       </c>
       <c r="R18" t="n">
-        <v>6860417</v>
+        <v>6860327</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2349,6 +2322,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2375,45 +2353,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129074919</v>
+        <v>129074106</v>
       </c>
       <c r="B19" t="n">
-        <v>78802</v>
+        <v>98727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469680</v>
+        <v>469787</v>
       </c>
       <c r="R19" t="n">
-        <v>6860506</v>
+        <v>6860379</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2472,10 +2459,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129074540</v>
+        <v>129075590</v>
       </c>
       <c r="B20" t="n">
-        <v>78052</v>
+        <v>78710</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2483,21 +2470,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2507,13 +2494,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469743</v>
+        <v>469576</v>
       </c>
       <c r="R20" t="n">
-        <v>6860415</v>
+        <v>6860411</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2569,10 +2556,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129075085</v>
+        <v>129072966</v>
       </c>
       <c r="B21" t="n">
-        <v>78710</v>
+        <v>79634</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2580,37 +2567,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469663</v>
+        <v>469711</v>
       </c>
       <c r="R21" t="n">
-        <v>6860504</v>
+        <v>6860337</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2666,10 +2653,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129073686</v>
+        <v>129240565</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>78833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2677,34 +2664,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469742</v>
+        <v>469806</v>
       </c>
       <c r="R22" t="n">
-        <v>6860327</v>
+        <v>6860413</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2731,17 +2718,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2768,54 +2750,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129074106</v>
+        <v>129240501</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>78833</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469787</v>
+        <v>469685</v>
       </c>
       <c r="R23" t="n">
-        <v>6860379</v>
+        <v>6860410</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2842,12 +2815,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2874,10 +2847,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129075590</v>
+        <v>129240555</v>
       </c>
       <c r="B24" t="n">
-        <v>78710</v>
+        <v>78741</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2905,17 +2878,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469576</v>
+        <v>469816</v>
       </c>
       <c r="R24" t="n">
-        <v>6860411</v>
+        <v>6860403</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2939,12 +2912,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2971,10 +2944,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129072966</v>
+        <v>129240472</v>
       </c>
       <c r="B25" t="n">
-        <v>79634</v>
+        <v>78741</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2982,21 +2955,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3006,13 +2979,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469711</v>
+        <v>469672</v>
       </c>
       <c r="R25" t="n">
-        <v>6860337</v>
+        <v>6860410</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3036,12 +3009,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3068,7 +3041,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129240565</v>
+        <v>129240219</v>
       </c>
       <c r="B26" t="n">
         <v>78833</v>
@@ -3103,10 +3076,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469806</v>
+        <v>469551</v>
       </c>
       <c r="R26" t="n">
-        <v>6860413</v>
+        <v>6860399</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3165,54 +3138,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129240619</v>
+        <v>129240407</v>
       </c>
       <c r="B27" t="n">
-        <v>98768</v>
+        <v>78741</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469801</v>
+        <v>469618</v>
       </c>
       <c r="R27" t="n">
-        <v>6860453</v>
+        <v>6860428</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3268,884 +3232,6 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>129240501</v>
-      </c>
-      <c r="B28" t="n">
-        <v>78833</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>469685</v>
-      </c>
-      <c r="R28" t="n">
-        <v>6860410</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Lillhärdal</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>129240256</v>
-      </c>
-      <c r="B29" t="n">
-        <v>79694</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>469555</v>
-      </c>
-      <c r="R29" t="n">
-        <v>6860433</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Lillhärdal</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>129240555</v>
-      </c>
-      <c r="B30" t="n">
-        <v>78741</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>353</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>469816</v>
-      </c>
-      <c r="R30" t="n">
-        <v>6860403</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Lillhärdal</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>129240241</v>
-      </c>
-      <c r="B31" t="n">
-        <v>78741</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>353</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>469557</v>
-      </c>
-      <c r="R31" t="n">
-        <v>6860436</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Lillhärdal</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>129240472</v>
-      </c>
-      <c r="B32" t="n">
-        <v>78741</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>353</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>469672</v>
-      </c>
-      <c r="R32" t="n">
-        <v>6860410</v>
-      </c>
-      <c r="S32" t="n">
-        <v>20</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Lillhärdal</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>129240219</v>
-      </c>
-      <c r="B33" t="n">
-        <v>78833</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>469551</v>
-      </c>
-      <c r="R33" t="n">
-        <v>6860399</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Lillhärdal</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>129242930</v>
-      </c>
-      <c r="B34" t="n">
-        <v>83044</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>469792</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6860485</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Lillhärdal</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>129243036</v>
-      </c>
-      <c r="B35" t="n">
-        <v>57735</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>469792</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6860485</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Lillhärdal</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>129240407</v>
-      </c>
-      <c r="B36" t="n">
-        <v>78741</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>353</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>469618</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6860428</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Lillhärdal</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129076566</v>
+        <v>129239886</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469689</v>
+        <v>469570</v>
       </c>
       <c r="R2" t="n">
-        <v>6860378</v>
+        <v>6860318</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129073324</v>
+        <v>129074218</v>
       </c>
       <c r="B3" t="n">
-        <v>78802</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469745</v>
+        <v>469807</v>
       </c>
       <c r="R3" t="n">
-        <v>6860335</v>
+        <v>6860393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129074721</v>
+        <v>129075085</v>
       </c>
       <c r="B4" t="n">
-        <v>78802</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469722</v>
+        <v>469663</v>
       </c>
       <c r="R4" t="n">
-        <v>6860490</v>
+        <v>6860504</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,59 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129073070</v>
+        <v>129075209</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469736</v>
+        <v>469625</v>
       </c>
       <c r="R5" t="n">
-        <v>6860324</v>
+        <v>6860485</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129074896</v>
+        <v>129075590</v>
       </c>
       <c r="B6" t="n">
-        <v>79663</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1117,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469691</v>
+        <v>469576</v>
       </c>
       <c r="R6" t="n">
-        <v>6860502</v>
+        <v>6860411</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1179,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129075167</v>
+        <v>129076255</v>
       </c>
       <c r="B7" t="n">
-        <v>78802</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1190,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1214,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469625</v>
+        <v>469608</v>
       </c>
       <c r="R7" t="n">
-        <v>6860490</v>
+        <v>6860373</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129076255</v>
+        <v>129240241</v>
       </c>
       <c r="B8" t="n">
-        <v>78710</v>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,14 +1288,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469608</v>
+        <v>469557</v>
       </c>
       <c r="R8" t="n">
-        <v>6860373</v>
+        <v>6860436</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1341,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129075209</v>
+        <v>129240283</v>
       </c>
       <c r="B9" t="n">
-        <v>78710</v>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,14 +1385,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469625</v>
+        <v>469547</v>
       </c>
       <c r="R9" t="n">
-        <v>6860485</v>
+        <v>6860448</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1438,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1470,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129074218</v>
+        <v>129240407</v>
       </c>
       <c r="B10" t="n">
-        <v>78710</v>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,14 +1482,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469807</v>
+        <v>469618</v>
       </c>
       <c r="R10" t="n">
-        <v>6860393</v>
+        <v>6860428</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1535,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1567,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129075376</v>
+        <v>129240472</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1578,37 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469623</v>
+        <v>469672</v>
       </c>
       <c r="R11" t="n">
-        <v>6860454</v>
+        <v>6860410</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1632,17 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1669,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129072852</v>
+        <v>129240555</v>
       </c>
       <c r="B12" t="n">
-        <v>78802</v>
+        <v>78993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1704,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469681</v>
+        <v>469816</v>
       </c>
       <c r="R12" t="n">
-        <v>6860335</v>
+        <v>6860403</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1734,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1766,45 +1742,59 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129074684</v>
+        <v>129073070</v>
       </c>
       <c r="B13" t="n">
-        <v>80177</v>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469714</v>
+        <v>469736</v>
       </c>
       <c r="R13" t="n">
-        <v>6860460</v>
+        <v>6860324</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,48 +1853,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129074551</v>
+        <v>129239971</v>
       </c>
       <c r="B14" t="n">
-        <v>79634</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469743</v>
+        <v>469513</v>
       </c>
       <c r="R14" t="n">
-        <v>6860417</v>
+        <v>6860345</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1928,12 +1918,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1960,45 +1950,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129074919</v>
+        <v>129242052</v>
       </c>
       <c r="B15" t="n">
-        <v>78802</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469680</v>
+        <v>469739</v>
       </c>
       <c r="R15" t="n">
-        <v>6860506</v>
+        <v>6860528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2025,12 +2015,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2057,10 +2047,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129074540</v>
+        <v>129242506</v>
       </c>
       <c r="B16" t="n">
-        <v>78052</v>
+        <v>83307</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2068,34 +2058,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6487</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469743</v>
+        <v>469752</v>
       </c>
       <c r="R16" t="n">
-        <v>6860415</v>
+        <v>6860517</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2122,12 +2112,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2154,10 +2144,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129075085</v>
+        <v>129073823</v>
       </c>
       <c r="B17" t="n">
-        <v>78710</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2165,21 +2155,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2189,13 +2179,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>469663</v>
+        <v>469769</v>
       </c>
       <c r="R17" t="n">
-        <v>6860504</v>
+        <v>6860351</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2251,10 +2241,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129073686</v>
+        <v>129074896</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2262,21 +2252,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469742</v>
+        <v>469691</v>
       </c>
       <c r="R18" t="n">
-        <v>6860327</v>
+        <v>6860502</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2322,11 +2312,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2353,57 +2338,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129074106</v>
+        <v>129075687</v>
       </c>
       <c r="B19" t="n">
-        <v>98727</v>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469787</v>
+        <v>469536</v>
       </c>
       <c r="R19" t="n">
-        <v>6860379</v>
+        <v>6860334</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2459,10 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129075590</v>
+        <v>129240256</v>
       </c>
       <c r="B20" t="n">
-        <v>78710</v>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2470,37 +2446,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lyckelsån, Lyckelsån, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469576</v>
+        <v>469555</v>
       </c>
       <c r="R20" t="n">
-        <v>6860411</v>
+        <v>6860433</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2524,12 +2500,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2556,10 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129072966</v>
+        <v>129240295</v>
       </c>
       <c r="B21" t="n">
-        <v>79634</v>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,21 +2543,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2591,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469711</v>
+        <v>469548</v>
       </c>
       <c r="R21" t="n">
-        <v>6860337</v>
+        <v>6860451</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2621,12 +2597,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2653,10 +2629,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129240565</v>
+        <v>129239994</v>
       </c>
       <c r="B22" t="n">
-        <v>78833</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2664,21 +2640,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2688,13 +2664,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469806</v>
+        <v>469498</v>
       </c>
       <c r="R22" t="n">
-        <v>6860413</v>
+        <v>6860348</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2750,45 +2726,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129240501</v>
+        <v>129074684</v>
       </c>
       <c r="B23" t="n">
-        <v>78833</v>
+        <v>80460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469685</v>
+        <v>469714</v>
       </c>
       <c r="R23" t="n">
-        <v>6860410</v>
+        <v>6860460</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2815,12 +2791,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2847,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129240555</v>
+        <v>129074540</v>
       </c>
       <c r="B24" t="n">
-        <v>78741</v>
+        <v>78334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2858,34 +2834,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469816</v>
+        <v>469743</v>
       </c>
       <c r="R24" t="n">
-        <v>6860403</v>
+        <v>6860415</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2912,12 +2888,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2944,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129240472</v>
+        <v>129073686</v>
       </c>
       <c r="B25" t="n">
-        <v>78741</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2955,37 +2931,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469672</v>
+        <v>469742</v>
       </c>
       <c r="R25" t="n">
-        <v>6860410</v>
+        <v>6860327</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3009,12 +2985,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3041,10 +3022,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129240219</v>
+        <v>129075376</v>
       </c>
       <c r="B26" t="n">
-        <v>78833</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3052,34 +3033,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469551</v>
+        <v>469623</v>
       </c>
       <c r="R26" t="n">
-        <v>6860399</v>
+        <v>6860454</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3106,12 +3087,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3138,10 +3124,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129240407</v>
+        <v>129076566</v>
       </c>
       <c r="B27" t="n">
-        <v>78741</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3149,34 +3135,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469618</v>
+        <v>469689</v>
       </c>
       <c r="R27" t="n">
-        <v>6860428</v>
+        <v>6860378</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3203,12 +3189,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3232,6 +3223,2125 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129240022</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>469488</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6860351</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129239926</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>469534</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6860333</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Noterat läte.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129073710</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>469757</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6860334</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129073789</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>469761</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6860341</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129074043</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>469786</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6860361</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129074106</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>469787</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6860379</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129075276</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>469602</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6860488</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129240619</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>469801</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6860453</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129240926</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>469750</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6860501</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129241030</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>469730</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6860526</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129242191</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>469744</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6860520</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129072852</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>469681</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6860335</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129073324</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>469745</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6860335</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129074721</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>469722</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6860490</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129074919</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>469680</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6860506</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129075167</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>469625</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6860490</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129240219</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>469551</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6860399</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129240501</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>469685</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6860410</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129240565</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>469806</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6860413</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129072966</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>469711</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6860337</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129074551</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lyckelsån, Lyckelsån, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>469743</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6860417</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47109-2025 artfynd.xlsx
+++ b/artfynd/A 47109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129239886</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129074218</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129075085</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129075209</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129075590</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129076255</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240241</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240283</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240407</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240472</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240555</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1850,6 +1910,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129073070</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1947,6 +2012,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129239971</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2044,6 +2114,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129242052</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2141,6 +2216,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129242506</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2238,6 +2318,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129073823</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2335,6 +2420,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129074896</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2432,6 +2522,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129075687</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2529,6 +2624,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240256</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2626,6 +2726,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240295</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2723,6 +2828,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129239994</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2820,6 +2930,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129074684</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2917,6 +3032,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129074540</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3019,6 +3139,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129073686</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3121,6 +3246,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129075376</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3223,6 +3353,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129076566</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3325,6 +3460,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240022</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3427,6 +3567,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129239926</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3533,6 +3678,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129073710</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3639,6 +3789,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129073789</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3745,6 +3900,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129074043</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3851,6 +4011,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129074106</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3948,6 +4113,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129075276</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4054,6 +4224,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240619</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4160,6 +4335,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240926</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4266,6 +4446,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129241030</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4372,6 +4557,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129242191</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4469,6 +4659,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129072852</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4566,6 +4761,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129073324</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4663,6 +4863,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129074721</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4760,6 +4965,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129074919</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4857,6 +5067,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129075167</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4954,6 +5169,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240219</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5051,6 +5271,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240501</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5148,6 +5373,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240565</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5245,6 +5475,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129072966</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5342,8 +5577,62 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129074551</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>